--- a/data/trending_integrated_20261007_13.xlsx
+++ b/data/trending_integrated_20261007_13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H2" t="n">
         <v>3.27</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26337761314</v>
+        <v>26348969214</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8130</v>
+        <v>8150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.44%</t>
+          <t>'+20.74%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G3" t="n">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>102735335565</v>
+        <v>105357273505</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -711,14 +711,14 @@
         <v>2890</v>
       </c>
       <c r="R3" t="n">
-        <v>-688000</v>
+        <v>-660000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 기대감. 건설 기초 소재 대장주.</t>
+          <t>정부의 건설 규제 완화 및 용적률 상향 정책 수혜 기대감. 거래량 증가 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '건설', '그린벨트']</t>
+          <t>['건설', '용적률', '규제 완화']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2795</v>
+        <v>2825</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.70%</t>
+          <t>'+17.95%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
         <v>1.36</v>
@@ -794,7 +794,7 @@
         <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>33731082269</v>
+        <v>34677876726</v>
       </c>
       <c r="P4" t="n">
         <v>6000</v>
@@ -803,14 +803,14 @@
         <v>1700</v>
       </c>
       <c r="R4" t="n">
-        <v>-46000</v>
+        <v>-147000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흑사병 관련주로 부각. 종근당바이오와 경쟁 구도 형성.</t>
+          <t>흑사병 관련주로 부각되며 급등. 전환사채 물량 출회 가능성 및 변동성 확대 우려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '바이오', '이슈']</t>
+          <t>['흑사병', '전환사채', '변동성']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26350</v>
+        <v>17420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.81%</t>
+          <t>'+17.15%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>246</v>
+        <v>275</v>
       </c>
       <c r="H5" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M5" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>95071552900</v>
+        <v>258740173355</v>
       </c>
       <c r="P5" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q5" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>223000</v>
+        <v>-94000</v>
       </c>
       <c r="S5" t="n">
-        <v>-202000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
+          <t>개인정보 유출 보안 이슈 부각. 양자보안 기술 기반 신규 공급 논의 및 미국 보안주 상승에 따른 기대감 형성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', 'IR']</t>
+          <t>['보안', '양자보안', '개인정보 유출']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16930</v>
+        <v>26100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.85%</t>
+          <t>'+13.73%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="F6" t="n">
-        <v>94</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>244871896630</v>
+        <v>95822128325</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R6" t="n">
-        <v>-83000</v>
+        <v>177000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-231000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인정보 유출 보안 이슈 부각. 양자보안 기술 관련 10곳 이상 공급 논의.</t>
+          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안', '양자보안', '개인정보 유출']</t>
+          <t>['유리기판', '주포', 'IR']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2615</v>
+        <v>2610</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.64%</t>
+          <t>'+9.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
         <v>69</v>
@@ -1070,7 +1070,7 @@
         <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>9297166428</v>
+        <v>9320176753</v>
       </c>
       <c r="P7" t="n">
         <v>4760</v>
@@ -1079,7 +1079,7 @@
         <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>-31000</v>
+        <v>5000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10550</v>
+        <v>10530</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.10%</t>
+          <t>'+8.89%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F8" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H8" t="n">
         <v>5.01</v>
@@ -1162,7 +1162,7 @@
         <v>4.84</v>
       </c>
       <c r="O8" t="n">
-        <v>17673597995</v>
+        <v>17789147010</v>
       </c>
       <c r="P8" t="n">
         <v>15900</v>
@@ -1171,7 +1171,7 @@
         <v>6310</v>
       </c>
       <c r="R8" t="n">
-        <v>-216000</v>
+        <v>-210000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13270</v>
+        <v>13220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.62%</t>
+          <t>'+7.22%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" t="n">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>177780286255</v>
+        <v>178572295650</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1263,23 +1263,23 @@
         <v>4020</v>
       </c>
       <c r="R9" t="n">
-        <v>-65000</v>
+        <v>-83000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼미금속, 가스터빈 블레이드 납품 개시 뉴스 기반 상승 기대. 변동성 속 매수 의견.</t>
+          <t>가스터빈 블레이드 납품 개시 뉴스 확인. 위꼬리 달성 후 차익실현 매물 출현 가능성 및 주포 이탈 가능성 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['가스터빈', '납품 개시', '매수']</t>
+          <t>['납품', '가스터빈', '뉴스']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5310</v>
+        <v>5190</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+5.99%</t>
+          <t>'+3.59%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G10" t="n">
         <v>381</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>218697709240</v>
+        <v>222643872540</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1355,7 +1355,7 @@
         <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>381000</v>
+        <v>123000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1391,83 +1391,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>272000</v>
+        <v>7000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.29%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>-0.77</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>481</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>1345</v>
+        <v>211</v>
       </c>
       <c r="H11" t="n">
-        <v>46.37</v>
+        <v>1.1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272000</v>
+        <v>6980</v>
       </c>
       <c r="K11" t="n">
-        <v>269500</v>
+        <v>7000</v>
       </c>
       <c r="L11" t="n">
-        <v>279500</v>
+        <v>7240</v>
       </c>
       <c r="M11" t="n">
-        <v>268500</v>
+        <v>6580</v>
       </c>
       <c r="N11" t="n">
-        <v>46.41</v>
+        <v>1.87</v>
       </c>
       <c r="O11" t="n">
-        <v>2651772450000</v>
+        <v>59132604160</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>11370</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>3300</v>
       </c>
       <c r="R11" t="n">
-        <v>1377000</v>
+        <v>29000</v>
       </c>
       <c r="S11" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매도세 지속. 정치적 이슈와 연관된 부정적 전망.</t>
+          <t>금융권 망분리 완화 정책 수혜 기대감. 라온시큐어 등 보안주 강세에 따른 동반 상승 가능성 및 거래량 부진.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['매도세', '기관', '정치']</t>
+          <t>['보안', '망분리', '금융권']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81000</v>
+        <v>271500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-0.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>298</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>161</v>
+        <v>483</v>
       </c>
       <c r="G12" t="n">
-        <v>748</v>
+        <v>1362</v>
       </c>
       <c r="H12" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K12" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L12" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M12" t="n">
-        <v>80600</v>
+        <v>268500</v>
       </c>
       <c r="N12" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>129817127950</v>
+        <v>2734923864000</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-8000</v>
+        <v>1438000</v>
       </c>
       <c r="S12" t="n">
-        <v>-36000</v>
+        <v>-173000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>구글의 미국 최대 원전기업 전력구매 계약에 따른 기대감, 주가 상승 및 공매도 청산 요구.</t>
+          <t>정치적 이슈에 따른 외국인 및 기관 매도세 지속. 실적 기대감에도 불구하고 주가 상승은 어려울 것이라는 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '전력구매', '구글']</t>
+          <t>['외국인', '기관', '실적']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,130 +1568,130 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17510</v>
+        <v>239000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.35%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>169</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="G13" t="n">
-        <v>331</v>
+        <v>901</v>
       </c>
       <c r="H13" t="n">
-        <v>9.5</v>
+        <v>4.12</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17750</v>
+        <v>241000</v>
       </c>
       <c r="K13" t="n">
-        <v>17970</v>
+        <v>253000</v>
       </c>
       <c r="L13" t="n">
-        <v>18030</v>
+        <v>257000</v>
       </c>
       <c r="M13" t="n">
-        <v>17420</v>
+        <v>233500</v>
       </c>
       <c r="N13" t="n">
-        <v>9.390000000000001</v>
+        <v>4.08</v>
       </c>
       <c r="O13" t="n">
-        <v>45008874465</v>
+        <v>84247457250</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>1233000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>120000</v>
       </c>
       <c r="R13" t="n">
-        <v>-177000</v>
+        <v>-72000</v>
       </c>
       <c r="S13" t="n">
-        <v>-36000</v>
+        <v>2000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상. 공매도 세력과의 경쟁.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '원전', '건설']</t>
+          <t>['인슐린', 'L/O', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13200</v>
+        <v>80800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.42%</t>
+          <t>'-0.86%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>303</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="G14" t="n">
-        <v>84</v>
+        <v>774</v>
       </c>
       <c r="H14" t="n">
-        <v>3.18</v>
+        <v>22.59</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>13390</v>
+        <v>81500</v>
       </c>
       <c r="K14" t="n">
-        <v>13770</v>
+        <v>83500</v>
       </c>
       <c r="L14" t="n">
-        <v>13830</v>
+        <v>84300</v>
       </c>
       <c r="M14" t="n">
-        <v>13080</v>
+        <v>80600</v>
       </c>
       <c r="N14" t="n">
-        <v>3.12</v>
+        <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>25218204220</v>
+        <v>132148431400</v>
       </c>
       <c r="P14" t="n">
-        <v>20300</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>3020</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-292000</v>
+        <v>-204000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>구글의 미국 원전 기업 전력 구매 계약 발표에 따른 수혜 기대감. 공매도 청산 및 단기 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['원전', '전력구매계약', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,135 +1747,135 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237500</v>
+        <v>17490</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.46%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="F15" t="n">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>894</v>
+        <v>335</v>
       </c>
       <c r="H15" t="n">
-        <v>4.12</v>
+        <v>9.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>241000</v>
+        <v>17750</v>
       </c>
       <c r="K15" t="n">
-        <v>253000</v>
+        <v>17970</v>
       </c>
       <c r="L15" t="n">
-        <v>257000</v>
+        <v>18030</v>
       </c>
       <c r="M15" t="n">
-        <v>233500</v>
+        <v>17420</v>
       </c>
       <c r="N15" t="n">
-        <v>4.08</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>83219594000</v>
+        <v>46008717840</v>
       </c>
       <c r="P15" t="n">
-        <v>1233000</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>120000</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-49000</v>
+        <v>-193000</v>
       </c>
       <c r="S15" t="n">
-        <v>2000</v>
+        <v>-40000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상. 공매도 세력과의 경쟁.</t>
+          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['인슐린', 'L/O', '공매도']</t>
+          <t>['수주', '원전', '건설']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1745000</v>
+        <v>13160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.58%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>439</v>
+        <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>1728</v>
+        <v>84</v>
       </c>
       <c r="H16" t="n">
-        <v>49.71</v>
+        <v>3.18</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,139 +1883,139 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1773000</v>
+        <v>13390</v>
       </c>
       <c r="K16" t="n">
-        <v>1728000</v>
+        <v>13770</v>
       </c>
       <c r="L16" t="n">
-        <v>1779000</v>
+        <v>13830</v>
       </c>
       <c r="M16" t="n">
-        <v>1725000</v>
+        <v>13080</v>
       </c>
       <c r="N16" t="n">
-        <v>49.76</v>
+        <v>3.12</v>
       </c>
       <c r="O16" t="n">
-        <v>2674629665000</v>
+        <v>25330660365</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q16" t="n">
-        <v>403000</v>
+        <v>3020</v>
       </c>
       <c r="R16" t="n">
-        <v>-199000</v>
+        <v>-312000</v>
       </c>
       <c r="S16" t="n">
-        <v>-57000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매도세 지속. 나스닥 지수 및 정치적 이슈 영향.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['매도세', '외국인', '정치']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18070</v>
+        <v>1742000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'-1.75%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>177</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>121</v>
+        <v>441</v>
       </c>
       <c r="G17" t="n">
-        <v>1004</v>
+        <v>1736</v>
       </c>
       <c r="H17" t="n">
-        <v>4.92</v>
+        <v>49.71</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18530</v>
+        <v>1773000</v>
       </c>
       <c r="K17" t="n">
-        <v>18950</v>
+        <v>1728000</v>
       </c>
       <c r="L17" t="n">
-        <v>19870</v>
+        <v>1779000</v>
       </c>
       <c r="M17" t="n">
-        <v>17880</v>
+        <v>1725000</v>
       </c>
       <c r="N17" t="n">
-        <v>3.81</v>
+        <v>49.76</v>
       </c>
       <c r="O17" t="n">
-        <v>270043528525</v>
+        <v>2733559278000</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>403000</v>
       </c>
       <c r="R17" t="n">
-        <v>-491000</v>
+        <v>-387000</v>
       </c>
       <c r="S17" t="n">
-        <v>2000</v>
+        <v>-80000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 강세 영향. 젠슨 황의 광통신 투자 언급.</t>
+          <t>외국인 매도세 지속 및 추세선 하향 돌파. 정치적 이슈에 따른 투자 심리 위축 및 실적 부진 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '미국 주가', '젠슨 황']</t>
+          <t>['외국인', '추세선', '실적']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6780</v>
+        <v>17960</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.87%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.77</v>
+        <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>182</v>
       </c>
       <c r="F18" t="n">
-        <v>55</v>
+        <v>125</v>
       </c>
       <c r="G18" t="n">
-        <v>206</v>
+        <v>1038</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1</v>
+        <v>4.92</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6980</v>
+        <v>18530</v>
       </c>
       <c r="K18" t="n">
-        <v>7000</v>
+        <v>18950</v>
       </c>
       <c r="L18" t="n">
-        <v>7240</v>
+        <v>19870</v>
       </c>
       <c r="M18" t="n">
-        <v>6580</v>
+        <v>17880</v>
       </c>
       <c r="N18" t="n">
-        <v>1.87</v>
+        <v>3.81</v>
       </c>
       <c r="O18" t="n">
-        <v>55422014375</v>
+        <v>271759278195</v>
       </c>
       <c r="P18" t="n">
-        <v>11370</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>3300</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>180000</v>
+        <v>-435000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 개선 기대에도 불구하고 주가 부진. 망분리 완화 정책 수혜 기대와 라온시큐어 비교 언급.</t>
+          <t>미국 광통신 주가 강세 영향. 젠슨 황의 광통신 투자 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['실적 개선', '망분리 완화', '주가 부진']</t>
+          <t>['광통신', '미국 주가', '젠슨 황']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45850</v>
+        <v>45800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F19" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G19" t="n">
-        <v>2170</v>
+        <v>2186</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>36244825600</v>
+        <v>36464616575</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2183,10 +2183,10 @@
         <v>24150</v>
       </c>
       <c r="R19" t="n">
+        <v>-17000</v>
+      </c>
+      <c r="S19" t="n">
         <v>3000</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30400</v>
+        <v>30200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.25%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H20" t="n">
         <v>10.78</v>
@@ -2266,7 +2266,7 @@
         <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>90200341225</v>
+        <v>91339436100</v>
       </c>
       <c r="P20" t="n">
         <v>75900</v>
@@ -2275,10 +2275,10 @@
         <v>15960</v>
       </c>
       <c r="R20" t="n">
-        <v>-540000</v>
+        <v>-635000</v>
       </c>
       <c r="S20" t="n">
-        <v>-24000</v>
+        <v>-35000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12370</v>
+        <v>12320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-5.30%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2332,7 +2332,7 @@
         <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="H21" t="n">
         <v>1.42</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>36839007775</v>
+        <v>37093139025</v>
       </c>
       <c r="P21" t="n">
         <v>22250</v>
@@ -2367,10 +2367,10 @@
         <v>6000</v>
       </c>
       <c r="R21" t="n">
-        <v>-101000</v>
+        <v>-170000</v>
       </c>
       <c r="S21" t="n">
-        <v>9000</v>
+        <v>13000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2397,6 +2397,98 @@
       <c r="Z21" t="inlineStr">
         <is>
           <t>047920</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>켄코아에어로스페이스</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12750</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-7.07%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E22" t="n">
+        <v>89</v>
+      </c>
+      <c r="F22" t="n">
+        <v>54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>130</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>13720</v>
+      </c>
+      <c r="K22" t="n">
+        <v>13650</v>
+      </c>
+      <c r="L22" t="n">
+        <v>14650</v>
+      </c>
+      <c r="M22" t="n">
+        <v>12720</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O22" t="n">
+        <v>54000285360</v>
+      </c>
+      <c r="P22" t="n">
+        <v>39600</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>7300</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-84000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>누리호 발사 성공에도 불구하고 주가 하락. 공매도 세력의 매도 압력 및 테마 소멸 우려.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['누리호', '공매도', '테마']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>274090</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261007_13.xlsx
+++ b/data/trending_integrated_20261007_13.xlsx
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26348969214</v>
+        <v>26352712564</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8150</v>
+        <v>8130</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.74%</t>
+          <t>'+20.44%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>105357273505</v>
+        <v>106524106330</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 건설 규제 완화 및 용적률 상향 정책 수혜 기대감. 거래량 증가 및 단기 급등 가능성 언급.</t>
+          <t>정부 규제 완화 정책 기대감 반영. 실거래량 증가 및 긍정적 차트 분석 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['건설', '용적률', '규제 완화']</t>
+          <t>['규제 완화', '거래량', '차트']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2825</v>
+        <v>2880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.95%</t>
+          <t>'+20.25%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="H4" t="n">
         <v>1.36</v>
@@ -794,7 +794,7 @@
         <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>34677876726</v>
+        <v>35914635698</v>
       </c>
       <c r="P4" t="n">
         <v>6000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흑사병 관련주로 부각되며 급등. 전환사채 물량 출회 가능성 및 변동성 확대 우려.</t>
+          <t>흑사병 관련 테마주 언급. 차익실현 및 보합세에 대한 우려와 기대 공존.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '전환사채', '변동성']</t>
+          <t>['흑사병', '테마주', '거래량']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17420</v>
+        <v>5190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.15%</t>
+          <t>'+17.95%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.98</v>
+        <v>3.32</v>
       </c>
       <c r="E5" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="F5" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37</v>
+        <v>4.72</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14870</v>
+        <v>4400</v>
       </c>
       <c r="K5" t="n">
-        <v>15480</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17590</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>14600</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>258740173355</v>
+        <v>223989000000</v>
       </c>
       <c r="P5" t="n">
-        <v>17590</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-94000</v>
+        <v>123000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 보안 이슈 부각. 양자보안 기술 기반 신규 공급 논의 및 미국 보안주 상승에 따른 기대감 형성.</t>
+          <t>미국 증시 강세와 연동된 긍정적 분위기. 2200억 규모 발주서 확보.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안', '양자보안', '개인정보 유출']</t>
+          <t>['발주서', '미국 증시', '주포']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26100</v>
+        <v>17250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+13.73%</t>
+          <t>'+16.01%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="F6" t="n">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="G6" t="n">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K6" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L6" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M6" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
-        <v>95822128325</v>
+        <v>263686033920</v>
       </c>
       <c r="P6" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q6" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>177000</v>
+        <v>-94000</v>
       </c>
       <c r="S6" t="n">
-        <v>-231000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
+          <t>개인정보 유출 보안 이슈 부각. 양자보안 기술 기반 신규 공급 논의 및 미국 보안주 상승에 따른 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', 'IR']</t>
+          <t>['보안', '양자보안', '개인정보 유출']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1011,43 +1011,43 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2610</v>
+        <v>26000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+13.29%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.29</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>254</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2385</v>
+        <v>22950</v>
       </c>
       <c r="K7" t="n">
-        <v>2510</v>
+        <v>26200</v>
       </c>
       <c r="L7" t="n">
-        <v>2900</v>
+        <v>27600</v>
       </c>
       <c r="M7" t="n">
-        <v>2505</v>
+        <v>25550</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>9320176753</v>
+        <v>96633192875</v>
       </c>
       <c r="P7" t="n">
-        <v>4760</v>
+        <v>30100</v>
       </c>
       <c r="Q7" t="n">
-        <v>973</v>
+        <v>11140</v>
       </c>
       <c r="R7" t="n">
-        <v>5000</v>
+        <v>177000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-231000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['유리기판', '주포', 'IR']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10530</v>
+        <v>2630</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.89%</t>
+          <t>'+10.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="E8" t="n">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>331</v>
+        <v>69</v>
       </c>
       <c r="H8" t="n">
-        <v>5.01</v>
+        <v>0.82</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9670</v>
+        <v>2385</v>
       </c>
       <c r="K8" t="n">
-        <v>11020</v>
+        <v>2510</v>
       </c>
       <c r="L8" t="n">
-        <v>11030</v>
+        <v>2900</v>
       </c>
       <c r="M8" t="n">
-        <v>10300</v>
+        <v>2505</v>
       </c>
       <c r="N8" t="n">
-        <v>4.84</v>
+        <v>1.11</v>
       </c>
       <c r="O8" t="n">
-        <v>17789147010</v>
+        <v>9358358458</v>
       </c>
       <c r="P8" t="n">
-        <v>15900</v>
+        <v>4760</v>
       </c>
       <c r="Q8" t="n">
-        <v>6310</v>
+        <v>973</v>
       </c>
       <c r="R8" t="n">
-        <v>-210000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>폐렴 및 흑사병 테마주로 분류. 러시아-페스트, 케냐-에볼라 관련 사망자 발생.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['페스트', '흑사병', '테마주']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,91 +1195,91 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13220</v>
+        <v>10490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+7.22%</t>
+          <t>'+8.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="F9" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="H9" t="n">
-        <v>0.79</v>
+        <v>5.01</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>12330</v>
+        <v>9670</v>
       </c>
       <c r="K9" t="n">
-        <v>12580</v>
+        <v>11020</v>
       </c>
       <c r="L9" t="n">
-        <v>14260</v>
+        <v>11030</v>
       </c>
       <c r="M9" t="n">
-        <v>12300</v>
+        <v>10300</v>
       </c>
       <c r="N9" t="n">
-        <v>0.48</v>
+        <v>4.84</v>
       </c>
       <c r="O9" t="n">
-        <v>178572295650</v>
+        <v>17856806370</v>
       </c>
       <c r="P9" t="n">
-        <v>20850</v>
+        <v>15900</v>
       </c>
       <c r="Q9" t="n">
-        <v>4020</v>
+        <v>6310</v>
       </c>
       <c r="R9" t="n">
-        <v>-83000</v>
+        <v>-210000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>가스터빈 블레이드 납품 개시 뉴스 확인. 위꼬리 달성 후 차익실현 매물 출현 가능성 및 주포 이탈 가능성 제기.</t>
+          <t>전염병 관련 테마주 부각. 사망자 발생 뉴스에 따른 단기 급등 기대 및 신중론 공존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['납품', '가스터빈', '뉴스']</t>
+          <t>['전염병', '테마주', '사망자']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5190</v>
+        <v>13270</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.59%</t>
+          <t>'+7.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3.32</v>
+        <v>0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>183</v>
+        <v>98</v>
       </c>
       <c r="F10" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="G10" t="n">
-        <v>381</v>
+        <v>204</v>
       </c>
       <c r="H10" t="n">
-        <v>4.72</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5010</v>
+        <v>12330</v>
       </c>
       <c r="K10" t="n">
-        <v>5120</v>
+        <v>12580</v>
       </c>
       <c r="L10" t="n">
-        <v>5990</v>
+        <v>14260</v>
       </c>
       <c r="M10" t="n">
-        <v>4950</v>
+        <v>12300</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4</v>
+        <v>0.48</v>
       </c>
       <c r="O10" t="n">
-        <v>222643872540</v>
+        <v>178935228350</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>20850</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>4020</v>
       </c>
       <c r="R10" t="n">
-        <v>123000</v>
+        <v>-83000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 강세와 연동된 긍정적 분위기. 2200억 규모 발주서 확보.</t>
+          <t>가스터빈 블레이드 납품 개시 뉴스 확인. 위꼬리 달성 후 차익실현 매물 출현 가능성 및 주포 이탈 가능성 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['발주서', '미국 증시', '주포']</t>
+          <t>['납품', '가스터빈', '뉴스']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7000</v>
+        <v>272000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.29%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.77</v>
+        <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>482</v>
       </c>
       <c r="G11" t="n">
-        <v>211</v>
+        <v>1376</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>46.37</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6980</v>
+        <v>272000</v>
       </c>
       <c r="K11" t="n">
-        <v>7000</v>
+        <v>269500</v>
       </c>
       <c r="L11" t="n">
-        <v>7240</v>
+        <v>279500</v>
       </c>
       <c r="M11" t="n">
-        <v>6580</v>
+        <v>268500</v>
       </c>
       <c r="N11" t="n">
-        <v>1.87</v>
+        <v>46.41</v>
       </c>
       <c r="O11" t="n">
-        <v>59132604160</v>
+        <v>2783511266250</v>
       </c>
       <c r="P11" t="n">
-        <v>11370</v>
+        <v>374500</v>
       </c>
       <c r="Q11" t="n">
-        <v>3300</v>
+        <v>90200</v>
       </c>
       <c r="R11" t="n">
-        <v>29000</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>금융권 망분리 완화 정책 수혜 기대감. 라온시큐어 등 보안주 강세에 따른 동반 상승 가능성 및 거래량 부진.</t>
+          <t>국가 정치적 이슈와 연관된 부정적 언급 다수. 실적 호재 언급 있으나 정치 이슈에 묻힘.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['보안', '망분리', '금융권']</t>
+          <t>['실적', '외국인', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>271500</v>
+        <v>6970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.18%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.04</v>
+        <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>483</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>1362</v>
+        <v>212</v>
       </c>
       <c r="H12" t="n">
-        <v>46.37</v>
+        <v>1.1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>272000</v>
+        <v>6980</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>7000</v>
       </c>
       <c r="L12" t="n">
-        <v>279500</v>
+        <v>7240</v>
       </c>
       <c r="M12" t="n">
-        <v>268500</v>
+        <v>6580</v>
       </c>
       <c r="N12" t="n">
-        <v>46.41</v>
+        <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>2734923864000</v>
+        <v>61773302560</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>11370</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>3300</v>
       </c>
       <c r="R12" t="n">
-        <v>1438000</v>
+        <v>29000</v>
       </c>
       <c r="S12" t="n">
-        <v>-173000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈에 따른 외국인 및 기관 매도세 지속. 실적 기대감에도 불구하고 주가 상승은 어려울 것이라는 전망.</t>
+          <t>금융권 망분리 완화 정책 수혜 기대감. 라온시큐어 등 보안주 강세에 따른 동반 상승 가능성 및 거래량 부진.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '실적']</t>
+          <t>['보안', '망분리', '금융권']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,86 +1568,86 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>239000</v>
+        <v>80900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>169</v>
+        <v>307</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="G13" t="n">
-        <v>901</v>
+        <v>803</v>
       </c>
       <c r="H13" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>241000</v>
+        <v>81500</v>
       </c>
       <c r="K13" t="n">
-        <v>253000</v>
+        <v>83500</v>
       </c>
       <c r="L13" t="n">
-        <v>257000</v>
+        <v>84300</v>
       </c>
       <c r="M13" t="n">
-        <v>233500</v>
+        <v>80600</v>
       </c>
       <c r="N13" t="n">
-        <v>4.08</v>
+        <v>22.56</v>
       </c>
       <c r="O13" t="n">
-        <v>84247457250</v>
+        <v>133455115550</v>
       </c>
       <c r="P13" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-72000</v>
+        <v>-204000</v>
       </c>
       <c r="S13" t="n">
-        <v>2000</v>
+        <v>-30000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상. 공매도 세력과의 경쟁.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 발표에 따른 두산에너빌리티 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['인슐린', 'L/O', '공매도']</t>
+          <t>['원전', '전력구매', '계약']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80800</v>
+        <v>238750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>303</v>
+        <v>177</v>
       </c>
       <c r="F14" t="n">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="G14" t="n">
-        <v>774</v>
+        <v>920</v>
       </c>
       <c r="H14" t="n">
-        <v>22.59</v>
+        <v>4.12</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>81500</v>
+        <v>241000</v>
       </c>
       <c r="K14" t="n">
-        <v>83500</v>
+        <v>253000</v>
       </c>
       <c r="L14" t="n">
-        <v>84300</v>
+        <v>257000</v>
       </c>
       <c r="M14" t="n">
-        <v>80600</v>
+        <v>233500</v>
       </c>
       <c r="N14" t="n">
-        <v>22.56</v>
+        <v>4.08</v>
       </c>
       <c r="O14" t="n">
-        <v>132148431400</v>
+        <v>84677878750</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>1233000</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>120000</v>
       </c>
       <c r="R14" t="n">
-        <v>-204000</v>
+        <v>-72000</v>
       </c>
       <c r="S14" t="n">
-        <v>-30000</v>
+        <v>2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 전력 구매 계약 발표에 따른 수혜 기대감. 공매도 청산 및 단기 급등 가능성 언급.</t>
+          <t>경구용 인슐린 10조원대 L/O 예상. 공매도 세력과의 경쟁.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '전력구매계약', '공매도']</t>
+          <t>['인슐린', 'L/O', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.46%</t>
+          <t>'-1.13%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1791,28 +1791,28 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17750</v>
+        <v>17690</v>
       </c>
       <c r="K15" t="n">
-        <v>17970</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>18030</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>17420</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>46008717840</v>
+        <v>46264000000</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-193000</v>
@@ -1855,18 +1855,18 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13160</v>
+        <v>13170</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-1.64%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
@@ -1898,7 +1898,7 @@
         <v>3.12</v>
       </c>
       <c r="O16" t="n">
-        <v>25330660365</v>
+        <v>25479317070</v>
       </c>
       <c r="P16" t="n">
         <v>20300</v>
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1742000</v>
+        <v>1744000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.75%</t>
+          <t>'-1.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G17" t="n">
-        <v>1736</v>
+        <v>1769</v>
       </c>
       <c r="H17" t="n">
         <v>49.71</v>
@@ -1990,7 +1990,7 @@
         <v>49.76</v>
       </c>
       <c r="O17" t="n">
-        <v>2733559278000</v>
+        <v>2788407988000</v>
       </c>
       <c r="P17" t="n">
         <v>2987000</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외국인 매도세 지속 및 추세선 하향 돌파. 정치적 이슈에 따른 투자 심리 위축 및 실적 부진 우려.</t>
+          <t>국가 정치적 이슈와 연관된 부정적 언급 다수. 외국인 매도세 및 추세선 이탈에 대한 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국인', '추세선', '실적']</t>
+          <t>['외국인', '추세선', '정치']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17960</v>
+        <v>18020</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-2.75%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F18" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G18" t="n">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="H18" t="n">
         <v>4.92</v>
@@ -2082,7 +2082,7 @@
         <v>3.81</v>
       </c>
       <c r="O18" t="n">
-        <v>271759278195</v>
+        <v>272549648210</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45800</v>
+        <v>45700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.38%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F19" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G19" t="n">
-        <v>2186</v>
+        <v>2176</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>36464616575</v>
+        <v>36848668450</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2219,184 +2219,184 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30200</v>
+        <v>12370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-4.92%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>1.88</v>
       </c>
       <c r="E20" t="n">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="G20" t="n">
-        <v>258</v>
+        <v>208</v>
       </c>
       <c r="H20" t="n">
-        <v>10.78</v>
+        <v>1.42</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>31750</v>
+        <v>13010</v>
       </c>
       <c r="K20" t="n">
-        <v>32600</v>
+        <v>12330</v>
       </c>
       <c r="L20" t="n">
-        <v>32850</v>
+        <v>13560</v>
       </c>
       <c r="M20" t="n">
-        <v>30050</v>
+        <v>12220</v>
       </c>
       <c r="N20" t="n">
-        <v>10.77</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>91339436100</v>
+        <v>37206294740</v>
       </c>
       <c r="P20" t="n">
-        <v>75900</v>
+        <v>22250</v>
       </c>
       <c r="Q20" t="n">
-        <v>15960</v>
+        <v>6000</v>
       </c>
       <c r="R20" t="n">
-        <v>-635000</v>
+        <v>-170000</v>
       </c>
       <c r="S20" t="n">
-        <v>-35000</v>
+        <v>13000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['급락', '매도', '비교']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12320</v>
+        <v>30150</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.30%</t>
+          <t>'-5.04%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.88</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
+        <v>119</v>
+      </c>
+      <c r="F21" t="n">
         <v>69</v>
       </c>
-      <c r="F21" t="n">
-        <v>54</v>
-      </c>
       <c r="G21" t="n">
-        <v>205</v>
+        <v>258</v>
       </c>
       <c r="H21" t="n">
-        <v>1.42</v>
+        <v>10.78</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13010</v>
+        <v>31750</v>
       </c>
       <c r="K21" t="n">
-        <v>12330</v>
+        <v>32600</v>
       </c>
       <c r="L21" t="n">
-        <v>13560</v>
+        <v>32850</v>
       </c>
       <c r="M21" t="n">
-        <v>12220</v>
+        <v>30050</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>37093139025</v>
+        <v>91919139450</v>
       </c>
       <c r="P21" t="n">
-        <v>22250</v>
+        <v>75900</v>
       </c>
       <c r="Q21" t="n">
-        <v>6000</v>
+        <v>15960</v>
       </c>
       <c r="R21" t="n">
-        <v>-170000</v>
+        <v>-635000</v>
       </c>
       <c r="S21" t="n">
-        <v>13000</v>
+        <v>-35000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['급락', '매도', '비교']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12750</v>
+        <v>12650</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.07%</t>
+          <t>'-7.80%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G22" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2444,13 +2444,13 @@
         <v>14650</v>
       </c>
       <c r="M22" t="n">
-        <v>12720</v>
+        <v>12600</v>
       </c>
       <c r="N22" t="n">
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>54000285360</v>
+        <v>54920673980</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>누리호 발사 성공에도 불구하고 주가 하락. 공매도 세력의 매도 압력 및 테마 소멸 우려.</t>
+          <t>누리호 발사 성공 관련 기대감과 재료 소멸 우려. 공매도 및 차익 실현 매물에 대한 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['누리호', '공매도', '테마']</t>
+          <t>['누리호', '공매도', '재료 소멸']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261007_13.xlsx
+++ b/data/trending_integrated_20261007_13.xlsx
@@ -578,7 +578,7 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
         <v>47</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26352712564</v>
+        <v>26363109774</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8130</v>
+        <v>8160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.44%</t>
+          <t>'+20.89%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.02</v>
       </c>
       <c r="E3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
         <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>389</v>
+        <v>421</v>
       </c>
       <c r="H3" t="n">
         <v>5.12</v>
@@ -702,7 +702,7 @@
         <v>5.14</v>
       </c>
       <c r="O3" t="n">
-        <v>106524106330</v>
+        <v>108194176820</v>
       </c>
       <c r="P3" t="n">
         <v>23500</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부 규제 완화 정책 기대감 반영. 실거래량 증가 및 긍정적 차트 분석 언급.</t>
+          <t>정부의 부동산 규제 완화 및 용적률 상향 소식에 따른 건설 경기 회복 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['규제 완화', '거래량', '차트']</t>
+          <t>['용적률', '그린벨트', '건설']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2880</v>
+        <v>2850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.25%</t>
+          <t>'+19.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
         <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>1.36</v>
@@ -794,7 +794,7 @@
         <v>1.31</v>
       </c>
       <c r="O4" t="n">
-        <v>35914635698</v>
+        <v>36653866506</v>
       </c>
       <c r="P4" t="n">
         <v>6000</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흑사병 관련 테마주 언급. 차익실현 및 보합세에 대한 우려와 기대 공존.</t>
+          <t>흑사병 관련주로 분류되었으나 뚜렷한 재료 소멸 및 주가 부진에 대한 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주', '거래량']</t>
+          <t>['흑사병', '재료소멸', '자전']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5190</v>
+        <v>17120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+17.95%</t>
+          <t>'+15.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.32</v>
+        <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>388</v>
+        <v>291</v>
       </c>
       <c r="H5" t="n">
-        <v>4.72</v>
+        <v>2.37</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4400</v>
+        <v>14870</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15480</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>17590</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>14600</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>223989000000</v>
+        <v>267310911395</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>17590</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>6320</v>
       </c>
       <c r="R5" t="n">
-        <v>123000</v>
+        <v>-94000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 증시 강세와 연동된 긍정적 분위기. 2200억 규모 발주서 확보.</t>
+          <t>연이은 보안 사고와 미국 보안주 강세에 따른 수혜 전망 및 양자보안 사업 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['발주서', '미국 증시', '주포']</t>
+          <t>['양자보안', '보안주', '해킹']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17250</v>
+        <v>25800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+16.01%</t>
+          <t>'+12.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="F6" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="H6" t="n">
-        <v>2.37</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14870</v>
+        <v>22950</v>
       </c>
       <c r="K6" t="n">
-        <v>15480</v>
+        <v>26200</v>
       </c>
       <c r="L6" t="n">
-        <v>17590</v>
+        <v>27600</v>
       </c>
       <c r="M6" t="n">
-        <v>14600</v>
+        <v>25550</v>
       </c>
       <c r="N6" t="n">
-        <v>1.39</v>
+        <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>263686033920</v>
+        <v>97508493150</v>
       </c>
       <c r="P6" t="n">
-        <v>17590</v>
+        <v>30100</v>
       </c>
       <c r="Q6" t="n">
-        <v>6320</v>
+        <v>11140</v>
       </c>
       <c r="R6" t="n">
-        <v>-94000</v>
+        <v>177000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-231000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>개인정보 유출 보안 이슈 부각. 양자보안 기술 기반 신규 공급 논의 및 미국 보안주 상승에 따른 기대감 형성.</t>
+          <t>유리 기판 기술력에 대한 긍정적 평가 및 주가 상승 기대감, 유상증자 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['보안', '양자보안', '개인정보 유출']</t>
+          <t>['유리기판', '주포', '유증']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26000</v>
+        <v>2615</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+13.29%</t>
+          <t>'+9.64%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>45</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>254</v>
+        <v>70</v>
       </c>
       <c r="H7" t="n">
-        <v>2.82</v>
+        <v>0.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>22950</v>
+        <v>2385</v>
       </c>
       <c r="K7" t="n">
-        <v>26200</v>
+        <v>2510</v>
       </c>
       <c r="L7" t="n">
-        <v>27600</v>
+        <v>2900</v>
       </c>
       <c r="M7" t="n">
-        <v>25550</v>
+        <v>2505</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>96633192875</v>
+        <v>9823397738</v>
       </c>
       <c r="P7" t="n">
-        <v>30100</v>
+        <v>4760</v>
       </c>
       <c r="Q7" t="n">
-        <v>11140</v>
+        <v>973</v>
       </c>
       <c r="R7" t="n">
-        <v>177000</v>
+        <v>5000</v>
       </c>
       <c r="S7" t="n">
-        <v>-231000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>유리 기술력 기반의 브로드컴, 인텔 뚫기 기대감. 주포 2천억 유입 및 3만원 돌파 가능성 언급.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', 'IR']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,86 +1108,86 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2630</v>
+        <v>10560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.27%</t>
+          <t>'+9.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.29</v>
+        <v>0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>69</v>
+        <v>351</v>
       </c>
       <c r="H8" t="n">
-        <v>0.82</v>
+        <v>5.01</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2385</v>
+        <v>9670</v>
       </c>
       <c r="K8" t="n">
-        <v>2510</v>
+        <v>11020</v>
       </c>
       <c r="L8" t="n">
-        <v>2900</v>
+        <v>11030</v>
       </c>
       <c r="M8" t="n">
-        <v>2505</v>
+        <v>10300</v>
       </c>
       <c r="N8" t="n">
-        <v>1.11</v>
+        <v>4.84</v>
       </c>
       <c r="O8" t="n">
-        <v>9358358458</v>
+        <v>17961683875</v>
       </c>
       <c r="P8" t="n">
-        <v>4760</v>
+        <v>15900</v>
       </c>
       <c r="Q8" t="n">
-        <v>973</v>
+        <v>6310</v>
       </c>
       <c r="R8" t="n">
-        <v>5000</v>
+        <v>-210000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>해외 질병 확산 관련 뉴스로 인한 테마주 기대감 형성. 다만, 해당 질병과 직접적인 관련성이 낮다는 분석도 존재.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['테마주', '질병', '확산']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1195,82 +1195,82 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10490</v>
+        <v>13410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.48%</t>
+          <t>'+8.76%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>339</v>
+        <v>210</v>
       </c>
       <c r="H9" t="n">
-        <v>5.01</v>
+        <v>0.79</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9670</v>
+        <v>12330</v>
       </c>
       <c r="K9" t="n">
-        <v>11020</v>
+        <v>12580</v>
       </c>
       <c r="L9" t="n">
-        <v>11030</v>
+        <v>14260</v>
       </c>
       <c r="M9" t="n">
-        <v>10300</v>
+        <v>12300</v>
       </c>
       <c r="N9" t="n">
-        <v>4.84</v>
+        <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>17856806370</v>
+        <v>184010467700</v>
       </c>
       <c r="P9" t="n">
-        <v>15900</v>
+        <v>20850</v>
       </c>
       <c r="Q9" t="n">
-        <v>6310</v>
+        <v>4020</v>
       </c>
       <c r="R9" t="n">
-        <v>-210000</v>
+        <v>-83000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>전염병 관련 테마주 부각. 사망자 발생 뉴스에 따른 단기 급등 기대 및 신중론 공존.</t>
+          <t>가스터빈 블레이드 납품 개시 소식에도 불구하고 주가 변동성 및 매도 의견 혼재.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전염병', '테마주', '사망자']</t>
+          <t>['납품', '가스터빈', '뉴스']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13270</v>
+        <v>5170</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+7.62%</t>
+          <t>'+3.19%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.31</v>
+        <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>98</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="G10" t="n">
-        <v>204</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>0.79</v>
+        <v>4.72</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12330</v>
+        <v>5010</v>
       </c>
       <c r="K10" t="n">
-        <v>12580</v>
+        <v>5120</v>
       </c>
       <c r="L10" t="n">
-        <v>14260</v>
+        <v>5990</v>
       </c>
       <c r="M10" t="n">
-        <v>12300</v>
+        <v>4950</v>
       </c>
       <c r="N10" t="n">
-        <v>0.48</v>
+        <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>178935228350</v>
+        <v>226554511065</v>
       </c>
       <c r="P10" t="n">
-        <v>20850</v>
+        <v>8100</v>
       </c>
       <c r="Q10" t="n">
-        <v>4020</v>
+        <v>592</v>
       </c>
       <c r="R10" t="n">
-        <v>-83000</v>
+        <v>123000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>가스터빈 블레이드 납품 개시 뉴스 확인. 위꼬리 달성 후 차익실현 매물 출현 가능성 및 주포 이탈 가능성 제기.</t>
+          <t>미국 증시 강세 및 대규모 선주문 발표에 따른 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['납품', '가스터빈', '뉴스']</t>
+          <t>['미국증시', '선주문', '주포']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>272000</v>
+        <v>241250</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>182</v>
       </c>
       <c r="F11" t="n">
-        <v>482</v>
+        <v>114</v>
       </c>
       <c r="G11" t="n">
-        <v>1376</v>
+        <v>963</v>
       </c>
       <c r="H11" t="n">
-        <v>46.37</v>
+        <v>4.12</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>272000</v>
+        <v>241000</v>
       </c>
       <c r="K11" t="n">
-        <v>269500</v>
+        <v>253000</v>
       </c>
       <c r="L11" t="n">
-        <v>279500</v>
+        <v>257000</v>
       </c>
       <c r="M11" t="n">
-        <v>268500</v>
+        <v>233500</v>
       </c>
       <c r="N11" t="n">
-        <v>46.41</v>
+        <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>2783511266250</v>
+        <v>86466683000</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>1233000</v>
       </c>
       <c r="Q11" t="n">
-        <v>90200</v>
+        <v>120000</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-72000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국가 정치적 이슈와 연관된 부정적 언급 다수. 실적 호재 언급 있으나 정치 이슈에 묻힘.</t>
+          <t>경구용 인슐린 및 아일리아 관련 기술 수출 기대감과 공매도 세력에 대한 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['실적', '외국인', '기관']</t>
+          <t>['경구용인슐린', '아일리아', '공매도']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6970</v>
+        <v>6980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.77</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="H12" t="n">
         <v>1.1</v>
@@ -1530,7 +1530,7 @@
         <v>1.87</v>
       </c>
       <c r="O12" t="n">
-        <v>61773302560</v>
+        <v>63383386825</v>
       </c>
       <c r="P12" t="n">
         <v>11370</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80900</v>
+        <v>271750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.74%</t>
+          <t>'-0.09%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E13" t="n">
-        <v>307</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>167</v>
+        <v>487</v>
       </c>
       <c r="G13" t="n">
-        <v>803</v>
+        <v>1420</v>
       </c>
       <c r="H13" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K13" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M13" t="n">
-        <v>80600</v>
+        <v>268500</v>
       </c>
       <c r="N13" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O13" t="n">
-        <v>133455115550</v>
+        <v>2852648957000</v>
       </c>
       <c r="P13" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-204000</v>
+        <v>1438000</v>
       </c>
       <c r="S13" t="n">
-        <v>-30000</v>
+        <v>-173000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 발표에 따른 두산에너빌리티 주가 상승 기대감.</t>
+          <t>정치적 언급과 함께 주가 하락 및 실적 기대에 대한 상반된 전망 혼재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['원전', '전력구매', '계약']</t>
+          <t>['실적', '개인투자자', '외국인']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,86 +1660,86 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>238750</v>
+        <v>81000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-0.61%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E14" t="n">
-        <v>177</v>
+        <v>304</v>
       </c>
       <c r="F14" t="n">
-        <v>114</v>
+        <v>164</v>
       </c>
       <c r="G14" t="n">
-        <v>920</v>
+        <v>798</v>
       </c>
       <c r="H14" t="n">
-        <v>4.12</v>
+        <v>22.59</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>241000</v>
+        <v>81500</v>
       </c>
       <c r="K14" t="n">
-        <v>253000</v>
+        <v>83500</v>
       </c>
       <c r="L14" t="n">
-        <v>257000</v>
+        <v>84300</v>
       </c>
       <c r="M14" t="n">
-        <v>233500</v>
+        <v>80600</v>
       </c>
       <c r="N14" t="n">
-        <v>4.08</v>
+        <v>22.56</v>
       </c>
       <c r="O14" t="n">
-        <v>84677878750</v>
+        <v>134588227650</v>
       </c>
       <c r="P14" t="n">
-        <v>1233000</v>
+        <v>139200</v>
       </c>
       <c r="Q14" t="n">
-        <v>120000</v>
+        <v>57000</v>
       </c>
       <c r="R14" t="n">
-        <v>-72000</v>
+        <v>-204000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-30000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>경구용 인슐린 10조원대 L/O 예상. 공매도 세력과의 경쟁.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 뉴스에 따른 기대감 형성. 공매도 세력에 대한 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['인슐린', 'L/O', '공매도']</t>
+          <t>['원전', '공매도', '계약']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17490</v>
+        <v>17510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.13%</t>
+          <t>'-1.35%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.11</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="H15" t="n">
         <v>9.5</v>
@@ -1791,28 +1791,28 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17690</v>
+        <v>17750</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>17970</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>18030</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>17420</v>
       </c>
       <c r="N15" t="n">
         <v>9.390000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>46264000000</v>
+        <v>46914728210</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
         <v>-193000</v>
@@ -1851,11 +1851,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13170</v>
+        <v>1744000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1863,19 +1863,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>431</v>
       </c>
       <c r="G16" t="n">
-        <v>84</v>
+        <v>1832</v>
       </c>
       <c r="H16" t="n">
-        <v>3.18</v>
+        <v>49.71</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13390</v>
+        <v>1773000</v>
       </c>
       <c r="K16" t="n">
-        <v>13770</v>
+        <v>1728000</v>
       </c>
       <c r="L16" t="n">
-        <v>13830</v>
+        <v>1779000</v>
       </c>
       <c r="M16" t="n">
-        <v>13080</v>
+        <v>1725000</v>
       </c>
       <c r="N16" t="n">
-        <v>3.12</v>
+        <v>49.76</v>
       </c>
       <c r="O16" t="n">
-        <v>25479317070</v>
+        <v>2860036252500</v>
       </c>
       <c r="P16" t="n">
-        <v>20300</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>3020</v>
+        <v>403000</v>
       </c>
       <c r="R16" t="n">
-        <v>-312000</v>
+        <v>-387000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-80000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>정치적 요인, 외국인 매도세, 공매도에 대한 불만과 함께 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['외인', '공매도', '추세']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1744000</v>
+        <v>13140</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.64%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>440</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>1769</v>
+        <v>84</v>
       </c>
       <c r="H17" t="n">
-        <v>49.71</v>
+        <v>3.18</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1773000</v>
+        <v>13390</v>
       </c>
       <c r="K17" t="n">
-        <v>1728000</v>
+        <v>13770</v>
       </c>
       <c r="L17" t="n">
-        <v>1779000</v>
+        <v>13830</v>
       </c>
       <c r="M17" t="n">
-        <v>1725000</v>
+        <v>13080</v>
       </c>
       <c r="N17" t="n">
-        <v>49.76</v>
+        <v>3.12</v>
       </c>
       <c r="O17" t="n">
-        <v>2788407988000</v>
+        <v>25579984600</v>
       </c>
       <c r="P17" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q17" t="n">
-        <v>403000</v>
+        <v>3020</v>
       </c>
       <c r="R17" t="n">
-        <v>-387000</v>
+        <v>-312000</v>
       </c>
       <c r="S17" t="n">
-        <v>-80000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>국가 정치적 이슈와 연관된 부정적 언급 다수. 외국인 매도세 및 추세선 이탈에 대한 우려.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외국인', '추세선', '정치']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18020</v>
+        <v>17960</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.75%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F18" t="n">
         <v>126</v>
       </c>
       <c r="G18" t="n">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H18" t="n">
         <v>4.92</v>
@@ -2082,7 +2082,7 @@
         <v>3.81</v>
       </c>
       <c r="O18" t="n">
-        <v>272549648210</v>
+        <v>273741232950</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45700</v>
+        <v>45550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.59%</t>
+          <t>'-3.90%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="F19" t="n">
         <v>188</v>
       </c>
       <c r="G19" t="n">
-        <v>2176</v>
+        <v>2210</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2168,13 +2168,13 @@
         <v>47850</v>
       </c>
       <c r="M19" t="n">
-        <v>45650</v>
+        <v>45450</v>
       </c>
       <c r="N19" t="n">
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>36848668450</v>
+        <v>38998827600</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2219,184 +2219,184 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12370</v>
+        <v>30200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.92%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.88</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
+        <v>120</v>
+      </c>
+      <c r="F20" t="n">
         <v>69</v>
       </c>
-      <c r="F20" t="n">
-        <v>54</v>
-      </c>
       <c r="G20" t="n">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="H20" t="n">
-        <v>1.42</v>
+        <v>10.78</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13010</v>
+        <v>31750</v>
       </c>
       <c r="K20" t="n">
-        <v>12330</v>
+        <v>32600</v>
       </c>
       <c r="L20" t="n">
-        <v>13560</v>
+        <v>32850</v>
       </c>
       <c r="M20" t="n">
-        <v>12220</v>
+        <v>30050</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>10.77</v>
       </c>
       <c r="O20" t="n">
-        <v>37206294740</v>
+        <v>92762186625</v>
       </c>
       <c r="P20" t="n">
-        <v>22250</v>
+        <v>75900</v>
       </c>
       <c r="Q20" t="n">
-        <v>6000</v>
+        <v>15960</v>
       </c>
       <c r="R20" t="n">
-        <v>-170000</v>
+        <v>-635000</v>
       </c>
       <c r="S20" t="n">
-        <v>13000</v>
+        <v>-35000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['급락', '매도', '비교']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30150</v>
+        <v>12310</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.04%</t>
+          <t>'-5.38%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01</v>
+        <v>1.88</v>
       </c>
       <c r="E21" t="n">
-        <v>119</v>
+        <v>70</v>
       </c>
       <c r="F21" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G21" t="n">
-        <v>258</v>
+        <v>213</v>
       </c>
       <c r="H21" t="n">
-        <v>10.78</v>
+        <v>1.42</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>31750</v>
+        <v>13010</v>
       </c>
       <c r="K21" t="n">
-        <v>32600</v>
+        <v>12330</v>
       </c>
       <c r="L21" t="n">
-        <v>32850</v>
+        <v>13560</v>
       </c>
       <c r="M21" t="n">
-        <v>30050</v>
+        <v>12220</v>
       </c>
       <c r="N21" t="n">
-        <v>10.77</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>91919139450</v>
+        <v>37387301875</v>
       </c>
       <c r="P21" t="n">
-        <v>75900</v>
+        <v>22250</v>
       </c>
       <c r="Q21" t="n">
-        <v>15960</v>
+        <v>6000</v>
       </c>
       <c r="R21" t="n">
-        <v>-635000</v>
+        <v>-170000</v>
       </c>
       <c r="S21" t="n">
-        <v>-35000</v>
+        <v>13000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['급락', '매도', '비교']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12650</v>
+        <v>12930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-7.80%</t>
+          <t>'-5.76%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="F22" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>54920673980</v>
+        <v>56195013845</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>누리호 발사 성공 관련 기대감과 재료 소멸 우려. 공매도 및 차익 실현 매물에 대한 언급.</t>
+          <t>누리호 발사 성공에도 불구하고 재료 소멸 및 주가 하락에 대한 우려.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['누리호', '공매도', '재료 소멸']</t>
+          <t>['누리호', '재료소멸', '공매']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261007_13.xlsx
+++ b/data/trending_integrated_20261007_13.xlsx
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26363109774</v>
+        <v>26369218744</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8160</v>
+        <v>2870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.89%</t>
+          <t>'+19.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>421</v>
+        <v>106</v>
       </c>
       <c r="H3" t="n">
-        <v>5.12</v>
+        <v>1.36</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>6750</v>
+        <v>2395</v>
       </c>
       <c r="K3" t="n">
-        <v>6710</v>
+        <v>2410</v>
       </c>
       <c r="L3" t="n">
-        <v>8450</v>
+        <v>3020</v>
       </c>
       <c r="M3" t="n">
-        <v>6690</v>
+        <v>2405</v>
       </c>
       <c r="N3" t="n">
-        <v>5.14</v>
+        <v>1.31</v>
       </c>
       <c r="O3" t="n">
-        <v>108194176820</v>
+        <v>37556782204</v>
       </c>
       <c r="P3" t="n">
-        <v>23500</v>
+        <v>6000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2890</v>
+        <v>1700</v>
       </c>
       <c r="R3" t="n">
-        <v>-660000</v>
+        <v>-147000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>정부의 부동산 규제 완화 및 용적률 상향 소식에 따른 건설 경기 회복 기대감.</t>
+          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '건설']</t>
+          <t>['흑사병', '테마주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>307750</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>국전</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2850</v>
+        <v>7990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+19.00%</t>
+          <t>'+18.37%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="H4" t="n">
-        <v>1.36</v>
+        <v>5.12</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2395</v>
+        <v>6750</v>
       </c>
       <c r="K4" t="n">
-        <v>2410</v>
+        <v>6710</v>
       </c>
       <c r="L4" t="n">
-        <v>3020</v>
+        <v>8450</v>
       </c>
       <c r="M4" t="n">
-        <v>2405</v>
+        <v>6690</v>
       </c>
       <c r="N4" t="n">
-        <v>1.31</v>
+        <v>5.14</v>
       </c>
       <c r="O4" t="n">
-        <v>36653866506</v>
+        <v>111069331665</v>
       </c>
       <c r="P4" t="n">
-        <v>6000</v>
+        <v>23500</v>
       </c>
       <c r="Q4" t="n">
-        <v>1700</v>
+        <v>2890</v>
       </c>
       <c r="R4" t="n">
-        <v>-147000</v>
+        <v>-660000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>흑사병 관련주로 분류되었으나 뚜렷한 재료 소멸 및 주가 부진에 대한 언급.</t>
+          <t>정부의 용적률 상향 및 그린벨트 해제 이슈. 성수동 개발 기대감과 함께 상승 초입이라는 분석 제시.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['흑사병', '재료소멸', '자전']</t>
+          <t>['용적률', '그린벨트', '개발']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17120</v>
+        <v>16960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.13%</t>
+          <t>'+14.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.98</v>
       </c>
       <c r="E5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="H5" t="n">
         <v>2.37</v>
@@ -886,7 +886,7 @@
         <v>1.39</v>
       </c>
       <c r="O5" t="n">
-        <v>267310911395</v>
+        <v>270481404175</v>
       </c>
       <c r="P5" t="n">
         <v>17590</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>연이은 보안 사고와 미국 보안주 강세에 따른 수혜 전망 및 양자보안 사업 기대.</t>
+          <t>개인정보 유출 등 보안 이슈 부각. 라온은 주포가 물량을 쥐고 있으며, 양자보안 공급 논의 등 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자보안', '보안주', '해킹']</t>
+          <t>['보안', '양자보안', '주포']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
         <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H6" t="n">
         <v>2.82</v>
@@ -978,7 +978,7 @@
         <v>2.42</v>
       </c>
       <c r="O6" t="n">
-        <v>97508493150</v>
+        <v>98351355800</v>
       </c>
       <c r="P6" t="n">
         <v>30100</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2615</v>
+        <v>2645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.64%</t>
+          <t>'+10.90%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.29</v>
       </c>
       <c r="E7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H7" t="n">
         <v>0.82</v>
@@ -1070,7 +1070,7 @@
         <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>9823397738</v>
+        <v>9955392766</v>
       </c>
       <c r="P7" t="n">
         <v>4760</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10560</v>
+        <v>10710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+10.75%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H8" t="n">
         <v>5.01</v>
@@ -1162,7 +1162,7 @@
         <v>4.84</v>
       </c>
       <c r="O8" t="n">
-        <v>17961683875</v>
+        <v>18378578070</v>
       </c>
       <c r="P8" t="n">
         <v>15900</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>해외 질병 확산 관련 뉴스로 인한 테마주 기대감 형성. 다만, 해당 질병과 직접적인 관련성이 낮다는 분석도 존재.</t>
+          <t>흑사병, 페스트 등 전염병 테마주로 강하게 부각. 다양한 질병 테마에 엮이는 다재다능함 언급 및 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['테마주', '질병', '확산']</t>
+          <t>['전염병', '테마주', '흑사병']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13410</v>
+        <v>13490</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+8.76%</t>
+          <t>'+9.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>184010467700</v>
+        <v>185920722710</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>가스터빈 블레이드 납품 개시 소식에도 불구하고 주가 변동성 및 매도 의견 혼재.</t>
+          <t>한화파워향 가스터빈 블레이드 납품 개시. 일부 매도 의견도 있으나, 추세 전환 및 매수 기회라는 긍정적 분석 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['납품', '가스터빈', '뉴스']</t>
+          <t>['납품', '가스터빈']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5170</v>
+        <v>5160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.19%</t>
+          <t>'+2.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F10" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G10" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>226554511065</v>
+        <v>227783102840</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>241250</v>
+        <v>242500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.10%</t>
+          <t>'+0.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>114</v>
       </c>
       <c r="G11" t="n">
-        <v>963</v>
+        <v>979</v>
       </c>
       <c r="H11" t="n">
         <v>4.12</v>
@@ -1438,7 +1438,7 @@
         <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>86466683000</v>
+        <v>88068633250</v>
       </c>
       <c r="P11" t="n">
         <v>1233000</v>
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6980</v>
+        <v>80800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.86%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.77</v>
+        <v>0.03</v>
       </c>
       <c r="E12" t="n">
-        <v>88</v>
+        <v>309</v>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>166</v>
       </c>
       <c r="G12" t="n">
-        <v>216</v>
+        <v>816</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1</v>
+        <v>22.59</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>6980</v>
+        <v>81500</v>
       </c>
       <c r="K12" t="n">
-        <v>7000</v>
+        <v>83500</v>
       </c>
       <c r="L12" t="n">
-        <v>7240</v>
+        <v>84300</v>
       </c>
       <c r="M12" t="n">
-        <v>6580</v>
+        <v>80600</v>
       </c>
       <c r="N12" t="n">
-        <v>1.87</v>
+        <v>22.56</v>
       </c>
       <c r="O12" t="n">
-        <v>63383386825</v>
+        <v>135502437750</v>
       </c>
       <c r="P12" t="n">
-        <v>11370</v>
+        <v>139200</v>
       </c>
       <c r="Q12" t="n">
-        <v>3300</v>
+        <v>57000</v>
       </c>
       <c r="R12" t="n">
-        <v>29000</v>
+        <v>-204000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>금융권 망분리 완화 정책 수혜 기대감. 라온시큐어 등 보안주 강세에 따른 동반 상승 가능성 및 거래량 부진.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 뉴스에 따른 기대감 형성. 공매도 세력에 대한 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['보안', '망분리', '금융권']</t>
+          <t>['원전', '공매도', '계약']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>271750</v>
+        <v>17500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.09%</t>
+          <t>'-1.41%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.04</v>
+        <v>0.11</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="F13" t="n">
-        <v>487</v>
+        <v>46</v>
       </c>
       <c r="G13" t="n">
-        <v>1420</v>
+        <v>376</v>
       </c>
       <c r="H13" t="n">
-        <v>46.37</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>272000</v>
+        <v>17750</v>
       </c>
       <c r="K13" t="n">
-        <v>269500</v>
+        <v>17970</v>
       </c>
       <c r="L13" t="n">
-        <v>279500</v>
+        <v>18030</v>
       </c>
       <c r="M13" t="n">
-        <v>268500</v>
+        <v>17420</v>
       </c>
       <c r="N13" t="n">
-        <v>46.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>2852648957000</v>
+        <v>47507004350</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>1438000</v>
+        <v>-193000</v>
       </c>
       <c r="S13" t="n">
-        <v>-173000</v>
+        <v>-40000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 주가 하락 및 실적 기대에 대한 상반된 전망 혼재.</t>
+          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '개인투자자', '외국인']</t>
+          <t>['수주', '원전', '건설']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1655,43 +1655,43 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>81000</v>
+        <v>271750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.61%</t>
+          <t>'-1.54%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>304</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>164</v>
+        <v>491</v>
       </c>
       <c r="G14" t="n">
-        <v>798</v>
+        <v>1404</v>
       </c>
       <c r="H14" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>81500</v>
+        <v>276000</v>
       </c>
       <c r="K14" t="n">
-        <v>83500</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>84300</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>80600</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O14" t="n">
-        <v>134588227650</v>
+        <v>2921334000000</v>
       </c>
       <c r="P14" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-204000</v>
+        <v>1438000</v>
       </c>
       <c r="S14" t="n">
-        <v>-30000</v>
+        <v>-173000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 뉴스에 따른 기대감 형성. 공매도 세력에 대한 기대감도 일부 존재.</t>
+          <t>연일 외국인/기관 매도세와 정치적 리스크 언급. 실적 전망은 110조 이상으로 긍정적이나, 주가 부진에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '계약']</t>
+          <t>['실적', '매도세']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17510</v>
+        <v>1743000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.35%</t>
+          <t>'-1.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.11</v>
+        <v>-0.05</v>
       </c>
       <c r="E15" t="n">
-        <v>76</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>45</v>
+        <v>428</v>
       </c>
       <c r="G15" t="n">
-        <v>360</v>
+        <v>1856</v>
       </c>
       <c r="H15" t="n">
-        <v>9.5</v>
+        <v>49.71</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,47 +1791,47 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17750</v>
+        <v>1773000</v>
       </c>
       <c r="K15" t="n">
-        <v>17970</v>
+        <v>1728000</v>
       </c>
       <c r="L15" t="n">
-        <v>18030</v>
+        <v>1779000</v>
       </c>
       <c r="M15" t="n">
-        <v>17420</v>
+        <v>1725000</v>
       </c>
       <c r="N15" t="n">
-        <v>9.390000000000001</v>
+        <v>49.76</v>
       </c>
       <c r="O15" t="n">
-        <v>46914728210</v>
+        <v>2933554226500</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>403000</v>
       </c>
       <c r="R15" t="n">
-        <v>-193000</v>
+        <v>-387000</v>
       </c>
       <c r="S15" t="n">
-        <v>-40000</v>
+        <v>-80000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
+          <t>외국인 매도세와 정치적 리스크 지속 언급. 추세선 하향 돌파 및 추가 하락 가능성 제기. 삼성전자와 비교하며 매수 고려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['수주', '원전', '건설']</t>
+          <t>['매도세', '추세선']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1839,95 +1839,95 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1744000</v>
+        <v>6860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.64%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.05</v>
+        <v>-0.77</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>431</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>1832</v>
+        <v>217</v>
       </c>
       <c r="H16" t="n">
-        <v>49.71</v>
+        <v>1.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1773000</v>
+        <v>6980</v>
       </c>
       <c r="K16" t="n">
-        <v>1728000</v>
+        <v>7000</v>
       </c>
       <c r="L16" t="n">
-        <v>1779000</v>
+        <v>7240</v>
       </c>
       <c r="M16" t="n">
-        <v>1725000</v>
+        <v>6580</v>
       </c>
       <c r="N16" t="n">
-        <v>49.76</v>
+        <v>1.87</v>
       </c>
       <c r="O16" t="n">
-        <v>2860036252500</v>
+        <v>65141240340</v>
       </c>
       <c r="P16" t="n">
-        <v>2987000</v>
+        <v>11370</v>
       </c>
       <c r="Q16" t="n">
-        <v>403000</v>
+        <v>3300</v>
       </c>
       <c r="R16" t="n">
-        <v>-387000</v>
+        <v>29000</v>
       </c>
       <c r="S16" t="n">
-        <v>-80000</v>
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>정치적 요인, 외국인 매도세, 공매도에 대한 불만과 함께 주가 하락 전망.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['외인', '공매도', '추세']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
         <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H17" t="n">
         <v>3.18</v>
@@ -1990,7 +1990,7 @@
         <v>3.12</v>
       </c>
       <c r="O17" t="n">
-        <v>25579984600</v>
+        <v>25742295810</v>
       </c>
       <c r="P17" t="n">
         <v>20300</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17960</v>
+        <v>17980</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-2.97%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.11</v>
       </c>
       <c r="E18" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F18" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G18" t="n">
-        <v>1046</v>
+        <v>1061</v>
       </c>
       <c r="H18" t="n">
         <v>4.92</v>
@@ -2082,7 +2082,7 @@
         <v>3.81</v>
       </c>
       <c r="O18" t="n">
-        <v>273741232950</v>
+        <v>274790788205</v>
       </c>
       <c r="P18" t="n">
         <v>31500</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45550</v>
+        <v>45650</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.90%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="F19" t="n">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G19" t="n">
-        <v>2210</v>
+        <v>2263</v>
       </c>
       <c r="H19" t="n">
         <v>14.12</v>
@@ -2174,7 +2174,7 @@
         <v>14.1</v>
       </c>
       <c r="O19" t="n">
-        <v>38998827600</v>
+        <v>39390431800</v>
       </c>
       <c r="P19" t="n">
         <v>69200</v>
@@ -2219,184 +2219,184 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30200</v>
+        <v>12380</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-4.84%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>1.88</v>
       </c>
       <c r="E20" t="n">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="H20" t="n">
-        <v>10.78</v>
+        <v>1.42</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>31750</v>
+        <v>13010</v>
       </c>
       <c r="K20" t="n">
-        <v>32600</v>
+        <v>12330</v>
       </c>
       <c r="L20" t="n">
-        <v>32850</v>
+        <v>13560</v>
       </c>
       <c r="M20" t="n">
-        <v>30050</v>
+        <v>12220</v>
       </c>
       <c r="N20" t="n">
-        <v>10.77</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>92762186625</v>
+        <v>37608768725</v>
       </c>
       <c r="P20" t="n">
-        <v>75900</v>
+        <v>22250</v>
       </c>
       <c r="Q20" t="n">
-        <v>15960</v>
+        <v>6000</v>
       </c>
       <c r="R20" t="n">
-        <v>-635000</v>
+        <v>-170000</v>
       </c>
       <c r="S20" t="n">
-        <v>-35000</v>
+        <v>13000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['급락', '매도', '비교']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>12310</v>
+        <v>30200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-5.38%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.88</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="F21" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G21" t="n">
-        <v>213</v>
+        <v>258</v>
       </c>
       <c r="H21" t="n">
-        <v>1.42</v>
+        <v>10.78</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>13010</v>
+        <v>31750</v>
       </c>
       <c r="K21" t="n">
-        <v>12330</v>
+        <v>32600</v>
       </c>
       <c r="L21" t="n">
-        <v>13560</v>
+        <v>32850</v>
       </c>
       <c r="M21" t="n">
-        <v>12220</v>
+        <v>30050</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>37387301875</v>
+        <v>93640848300</v>
       </c>
       <c r="P21" t="n">
-        <v>22250</v>
+        <v>75900</v>
       </c>
       <c r="Q21" t="n">
-        <v>6000</v>
+        <v>15960</v>
       </c>
       <c r="R21" t="n">
-        <v>-170000</v>
+        <v>-635000</v>
       </c>
       <c r="S21" t="n">
-        <v>13000</v>
+        <v>-35000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['급락', '매도', '비교']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12930</v>
+        <v>12860</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-5.76%</t>
+          <t>'-6.27%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2450,7 +2450,7 @@
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>56195013845</v>
+        <v>56621867025</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>누리호 발사 성공에도 불구하고 재료 소멸 및 주가 하락에 대한 우려.</t>
+          <t>우주항공 테마로 언급되며 발사 성공 재료 소멸 우려. 공매도 및 높은 변동성에 대한 불안감 표출.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['누리호', '재료소멸', '공매']</t>
+          <t>['우주항공', '재료소멸']</t>
         </is>
       </c>
       <c r="X22" t="n">

--- a/data/trending_integrated_20261007_13.xlsx
+++ b/data/trending_integrated_20261007_13.xlsx
@@ -578,10 +578,10 @@
         <v>-0.08</v>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" t="n">
         <v>52</v>
@@ -610,7 +610,7 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>26369218744</v>
+        <v>26370295234</v>
       </c>
       <c r="P2" t="n">
         <v>5470</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>국전</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2870</v>
+        <v>2815</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.83%</t>
+          <t>'+18.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.29</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="G3" t="n">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2395</v>
+        <v>2385</v>
       </c>
       <c r="K3" t="n">
-        <v>2410</v>
+        <v>2510</v>
       </c>
       <c r="L3" t="n">
-        <v>3020</v>
+        <v>2900</v>
       </c>
       <c r="M3" t="n">
-        <v>2405</v>
+        <v>2505</v>
       </c>
       <c r="N3" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="O3" t="n">
-        <v>37556782204</v>
+        <v>12657704407</v>
       </c>
       <c r="P3" t="n">
-        <v>6000</v>
+        <v>4760</v>
       </c>
       <c r="Q3" t="n">
-        <v>1700</v>
+        <v>973</v>
       </c>
       <c r="R3" t="n">
-        <v>-147000</v>
+        <v>5000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
+          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['흑사병', '테마주']</t>
+          <t>['바이오', '유상증자', '기술적 반등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,12 +735,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>307750</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7990</v>
+        <v>7950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.37%</t>
+          <t>'+17.78%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="H4" t="n">
         <v>5.12</v>
@@ -794,7 +794,7 @@
         <v>5.14</v>
       </c>
       <c r="O4" t="n">
-        <v>111069331665</v>
+        <v>116030148720</v>
       </c>
       <c r="P4" t="n">
         <v>23500</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정부의 용적률 상향 및 그린벨트 해제 이슈. 성수동 개발 기대감과 함께 상승 초입이라는 분석 제시.</t>
+          <t>정부 규제 완화 및 용적률 상향 관련 뉴스. 성수동 재개발 기대감과 함께 급등.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['용적률', '그린벨트', '개발']</t>
+          <t>['용적률', '그린벨트', '재개발']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>국전</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16960</v>
+        <v>2820</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.06%</t>
+          <t>'+17.75%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.98</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="F5" t="n">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>297</v>
+        <v>106</v>
       </c>
       <c r="H5" t="n">
-        <v>2.37</v>
+        <v>1.36</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,47 +871,47 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>14870</v>
+        <v>2395</v>
       </c>
       <c r="K5" t="n">
-        <v>15480</v>
+        <v>2410</v>
       </c>
       <c r="L5" t="n">
-        <v>17590</v>
+        <v>3020</v>
       </c>
       <c r="M5" t="n">
-        <v>14600</v>
+        <v>2405</v>
       </c>
       <c r="N5" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>270481404175</v>
+        <v>38180495105</v>
       </c>
       <c r="P5" t="n">
-        <v>17590</v>
+        <v>6000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6320</v>
+        <v>1700</v>
       </c>
       <c r="R5" t="n">
-        <v>-94000</v>
+        <v>-147000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인정보 유출 등 보안 이슈 부각. 라온은 주포가 물량을 쥐고 있으며, 양자보안 공급 논의 등 긍정적 전망 제시.</t>
+          <t>흑사병 테마 관련주로 언급되며 거래량은 터졌으나 큰 상승은 못함. 반도체/이차전지 소재 업체로 변신 시도 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['보안', '양자보안', '주포']</t>
+          <t>['흑사병', '테마주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>307750</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25800</v>
+        <v>16950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+12.42%</t>
+          <t>'+13.99%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>0.98</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="G6" t="n">
-        <v>261</v>
+        <v>313</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>2.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,47 +963,47 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>22950</v>
+        <v>14870</v>
       </c>
       <c r="K6" t="n">
-        <v>26200</v>
+        <v>15480</v>
       </c>
       <c r="L6" t="n">
-        <v>27600</v>
+        <v>17590</v>
       </c>
       <c r="M6" t="n">
-        <v>25550</v>
+        <v>14600</v>
       </c>
       <c r="N6" t="n">
-        <v>2.42</v>
+        <v>1.39</v>
       </c>
       <c r="O6" t="n">
-        <v>98351355800</v>
+        <v>273257471115</v>
       </c>
       <c r="P6" t="n">
-        <v>30100</v>
+        <v>17590</v>
       </c>
       <c r="Q6" t="n">
-        <v>11140</v>
+        <v>6320</v>
       </c>
       <c r="R6" t="n">
-        <v>177000</v>
+        <v>-94000</v>
       </c>
       <c r="S6" t="n">
-        <v>-231000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리 기판 기술력에 대한 긍정적 평가 및 주가 상승 기대감, 유상증자 우려.</t>
+          <t>연이은 개인정보 유출 사고로 보안주 부각. 양자보안 기술력 및 대규모 공급 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', '주포', '유증']</t>
+          <t>['보안', '양자보안', '해킹']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2645</v>
+        <v>25850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+10.90%</t>
+          <t>'+12.64%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.29</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="H7" t="n">
-        <v>0.82</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2385</v>
+        <v>22950</v>
       </c>
       <c r="K7" t="n">
-        <v>2510</v>
+        <v>26200</v>
       </c>
       <c r="L7" t="n">
-        <v>2900</v>
+        <v>27600</v>
       </c>
       <c r="M7" t="n">
-        <v>2505</v>
+        <v>25550</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>9955392766</v>
+        <v>99087893725</v>
       </c>
       <c r="P7" t="n">
-        <v>4760</v>
+        <v>30100</v>
       </c>
       <c r="Q7" t="n">
-        <v>973</v>
+        <v>11140</v>
       </c>
       <c r="R7" t="n">
-        <v>5000</v>
+        <v>177000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-231000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>바이오 섹터 전반의 부진 속에서의 기술적 반등 시도. 유상증자 관련 지분 매각 이슈.</t>
+          <t>유리 기술력 기반 성장 기대감. 브로드컴, 씨게이트 등 대기업과의 협력 가능성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['바이오', '유상증자', '기술적 반등']</t>
+          <t>['유리', '기술력', '협력']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>204270</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10710</v>
+        <v>10850</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+10.75%</t>
+          <t>'+12.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.17</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="H8" t="n">
         <v>5.01</v>
@@ -1162,7 +1162,7 @@
         <v>4.84</v>
       </c>
       <c r="O8" t="n">
-        <v>18378578070</v>
+        <v>20099513235</v>
       </c>
       <c r="P8" t="n">
         <v>15900</v>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>흑사병, 페스트 등 전염병 테마주로 강하게 부각. 다양한 질병 테마에 엮이는 다재다능함 언급 및 상승 기대감 표출.</t>
+          <t>페스트, 에볼라 등 전염병 확산 관련주로 주목받으며 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13490</v>
+        <v>13260</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+9.41%</t>
+          <t>'+7.54%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.31</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F9" t="n">
         <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H9" t="n">
         <v>0.79</v>
@@ -1254,7 +1254,7 @@
         <v>0.48</v>
       </c>
       <c r="O9" t="n">
-        <v>185920722710</v>
+        <v>188059619680</v>
       </c>
       <c r="P9" t="n">
         <v>20850</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>한화파워향 가스터빈 블레이드 납품 개시. 일부 매도 의견도 있으나, 추세 전환 및 매수 기회라는 긍정적 분석 제시.</t>
+          <t>가스터빈 블레이드 첫 납품 뉴스 확인. 불확실성 해소 및 원전 투자 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['납품', '가스터빈']</t>
+          <t>['납품', '가스터빈', '원전']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5160</v>
+        <v>5150</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.99%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3.32</v>
       </c>
       <c r="E10" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F10" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G10" t="n">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="H10" t="n">
         <v>4.72</v>
@@ -1346,7 +1346,7 @@
         <v>1.4</v>
       </c>
       <c r="O10" t="n">
-        <v>227783102840</v>
+        <v>228883655930</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 강세 및 대규모 선주문 발표에 따른 주가 상승 기대감.</t>
+          <t>해외 기술주 강세와 연동되는 흐름. 대규모 선주문 규모 확인 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['미국증시', '선주문', '주포']</t>
+          <t>['기술주', '선주문', '상승']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G11" t="n">
-        <v>979</v>
+        <v>1009</v>
       </c>
       <c r="H11" t="n">
         <v>4.12</v>
@@ -1438,7 +1438,7 @@
         <v>4.08</v>
       </c>
       <c r="O11" t="n">
-        <v>88068633250</v>
+        <v>88989016000</v>
       </c>
       <c r="P11" t="n">
         <v>1233000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>경구용 인슐린 및 아일리아 관련 기술 수출 기대감과 공매도 세력에 대한 언급.</t>
+          <t>아일리아 성공 및 경구용 인슐린 10조원대 L/O 예상, 캐나다 건 계약 임박.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['경구용인슐린', '아일리아', '공매도']</t>
+          <t>['아일리아', '경구용 인슐린', '계약공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80800</v>
+        <v>271000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-0.37%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>309</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>166</v>
+        <v>485</v>
       </c>
       <c r="G12" t="n">
-        <v>816</v>
+        <v>1405</v>
       </c>
       <c r="H12" t="n">
-        <v>22.59</v>
+        <v>46.37</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>81500</v>
+        <v>272000</v>
       </c>
       <c r="K12" t="n">
-        <v>83500</v>
+        <v>269500</v>
       </c>
       <c r="L12" t="n">
-        <v>84300</v>
+        <v>279500</v>
       </c>
       <c r="M12" t="n">
-        <v>80600</v>
+        <v>268500</v>
       </c>
       <c r="N12" t="n">
-        <v>22.56</v>
+        <v>46.41</v>
       </c>
       <c r="O12" t="n">
-        <v>135502437750</v>
+        <v>2983629860000</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-204000</v>
+        <v>1438000</v>
       </c>
       <c r="S12" t="n">
-        <v>-30000</v>
+        <v>-173000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 뉴스에 따른 기대감 형성. 공매도 세력에 대한 기대감도 일부 존재.</t>
+          <t>연일 기관 및 외인 매도세와 정치적 이슈 언급. 실적 호조 기대감 있으나, 매도 압력 지속.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '계약']</t>
+          <t>['기관', '외인', '매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17500</v>
+        <v>80700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.41%</t>
+          <t>'-0.98%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.11</v>
+        <v>0.03</v>
       </c>
       <c r="E13" t="n">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="F13" t="n">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="G13" t="n">
-        <v>376</v>
+        <v>828</v>
       </c>
       <c r="H13" t="n">
-        <v>9.5</v>
+        <v>22.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17750</v>
+        <v>81500</v>
       </c>
       <c r="K13" t="n">
-        <v>17970</v>
+        <v>83500</v>
       </c>
       <c r="L13" t="n">
-        <v>18030</v>
+        <v>84300</v>
       </c>
       <c r="M13" t="n">
-        <v>17420</v>
+        <v>80600</v>
       </c>
       <c r="N13" t="n">
-        <v>9.390000000000001</v>
+        <v>22.56</v>
       </c>
       <c r="O13" t="n">
-        <v>47507004350</v>
+        <v>138023201550</v>
       </c>
       <c r="P13" t="n">
-        <v>40350</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>3320</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-193000</v>
+        <v>-204000</v>
       </c>
       <c r="S13" t="n">
-        <v>-40000</v>
+        <v>-30000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>올해 수주 목표 27조 및 미국 원전 건설 관련 긍정적 분위기 언급. 싱가포르 수상 및 미국 원전 수주 기대감. 주주들에게 호소하는 내용 다수 포함.</t>
+          <t>구글의 미국 원전 기업 컨스텔레이션과의 전력 구매 계약 뉴스에 따른 기대감 형성. 공매도 세력에 대한 기대감도 일부 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주', '원전', '건설']</t>
+          <t>['원전', '공매도', '계약']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>271750</v>
+        <v>17510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-1.54%</t>
+          <t>'-1.35%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>0.11</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>491</v>
+        <v>48</v>
       </c>
       <c r="G14" t="n">
-        <v>1404</v>
+        <v>387</v>
       </c>
       <c r="H14" t="n">
-        <v>46.37</v>
+        <v>9.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>276000</v>
+        <v>17750</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>17970</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>18030</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>17420</v>
       </c>
       <c r="N14" t="n">
-        <v>46.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>2921334000000</v>
+        <v>48139049000</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>1438000</v>
+        <v>-193000</v>
       </c>
       <c r="S14" t="n">
-        <v>-173000</v>
+        <v>-40000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>연일 외국인/기관 매도세와 정치적 리스크 언급. 실적 전망은 110조 이상으로 긍정적이나, 주가 부진에 대한 불만 표출.</t>
+          <t>미국 원전 건설 호재 및 수주 목표 달성 기대감. 주주 호소 및 긍정적 전망 다수.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '매도세']</t>
+          <t>['원전', '수주', '주주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>아톤</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1743000</v>
+        <v>6860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-1.69%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.05</v>
+        <v>-0.77</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>428</v>
+        <v>58</v>
       </c>
       <c r="G15" t="n">
-        <v>1856</v>
+        <v>223</v>
       </c>
       <c r="H15" t="n">
-        <v>49.71</v>
+        <v>1.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1773000</v>
+        <v>6980</v>
       </c>
       <c r="K15" t="n">
-        <v>1728000</v>
+        <v>7000</v>
       </c>
       <c r="L15" t="n">
-        <v>1779000</v>
+        <v>7240</v>
       </c>
       <c r="M15" t="n">
-        <v>1725000</v>
+        <v>6580</v>
       </c>
       <c r="N15" t="n">
-        <v>49.76</v>
+        <v>1.87</v>
       </c>
       <c r="O15" t="n">
-        <v>2933554226500</v>
+        <v>65947877600</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>11370</v>
       </c>
       <c r="Q15" t="n">
-        <v>403000</v>
+        <v>3300</v>
       </c>
       <c r="R15" t="n">
-        <v>-387000</v>
+        <v>29000</v>
       </c>
       <c r="S15" t="n">
-        <v>-80000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>외국인 매도세와 정치적 리스크 지속 언급. 추세선 하향 돌파 및 추가 하락 가능성 제기. 삼성전자와 비교하며 매수 고려.</t>
+          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['매도세', '추세선']</t>
+          <t>['보안', '금융권']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,130 +1844,130 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>158430</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>아톤</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6860</v>
+        <v>13110</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-1.72%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.77</v>
+        <v>0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="G16" t="n">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1</v>
+        <v>3.18</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>6980</v>
+        <v>13390</v>
       </c>
       <c r="K16" t="n">
-        <v>7000</v>
+        <v>13770</v>
       </c>
       <c r="L16" t="n">
-        <v>7240</v>
+        <v>13830</v>
       </c>
       <c r="M16" t="n">
-        <v>6580</v>
+        <v>13080</v>
       </c>
       <c r="N16" t="n">
-        <v>1.87</v>
+        <v>3.12</v>
       </c>
       <c r="O16" t="n">
-        <v>65141240340</v>
+        <v>25826286640</v>
       </c>
       <c r="P16" t="n">
-        <v>11370</v>
+        <v>20300</v>
       </c>
       <c r="Q16" t="n">
-        <v>3300</v>
+        <v>3020</v>
       </c>
       <c r="R16" t="n">
-        <v>29000</v>
+        <v>-312000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>보안주로 분류되며 금융권 공략 뉴스 부각. 라온시큐어와의 비교 언급 및 거래량 대비 주가 움직임에 대한 아쉬움 표출.</t>
+          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['보안', '금융권']</t>
+          <t>['전선주', '박스권', '공매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>158430</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13140</v>
+        <v>1736000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>426</v>
       </c>
       <c r="G17" t="n">
-        <v>85</v>
+        <v>1880</v>
       </c>
       <c r="H17" t="n">
-        <v>3.18</v>
+        <v>49.71</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13390</v>
+        <v>1773000</v>
       </c>
       <c r="K17" t="n">
-        <v>13770</v>
+        <v>1728000</v>
       </c>
       <c r="L17" t="n">
-        <v>13830</v>
+        <v>1779000</v>
       </c>
       <c r="M17" t="n">
-        <v>13080</v>
+        <v>1725000</v>
       </c>
       <c r="N17" t="n">
-        <v>3.12</v>
+        <v>49.76</v>
       </c>
       <c r="O17" t="n">
-        <v>25742295810</v>
+        <v>3014414157000</v>
       </c>
       <c r="P17" t="n">
-        <v>20300</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3020</v>
+        <v>403000</v>
       </c>
       <c r="R17" t="n">
-        <v>-312000</v>
+        <v>-387000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-80000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>최근 주가 하락 및 박스권 흐름에 대한 답답함 표출. 공매도 및 외국인 매도에 대한 의심.</t>
+          <t>지속적인 외인 매도와 정치적 이슈 언급. 시장 전반의 하락 추세 및 투자 심리 위축.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['전선주', '박스권', '공매도']</t>
+          <t>['외인', '매도', '추세']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17980</v>
+        <v>12660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-2.97%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.11</v>
+        <v>1.88</v>
       </c>
       <c r="E18" t="n">
-        <v>188</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="G18" t="n">
-        <v>1061</v>
+        <v>221</v>
       </c>
       <c r="H18" t="n">
-        <v>4.92</v>
+        <v>1.42</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,91 +2067,91 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>18530</v>
+        <v>13010</v>
       </c>
       <c r="K18" t="n">
-        <v>18950</v>
+        <v>12330</v>
       </c>
       <c r="L18" t="n">
-        <v>19870</v>
+        <v>13560</v>
       </c>
       <c r="M18" t="n">
-        <v>17880</v>
+        <v>12220</v>
       </c>
       <c r="N18" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>274790788205</v>
+        <v>38534038390</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>22250</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>6000</v>
       </c>
       <c r="R18" t="n">
-        <v>-435000</v>
+        <v>-170000</v>
       </c>
       <c r="S18" t="n">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 강세 영향. 젠슨 황의 광통신 투자 언급.</t>
+          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '미국 주가', '젠슨 황']</t>
+          <t>['유증', '신주상장', '자사주매집']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45650</v>
+        <v>17960</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.69%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.02</v>
+        <v>1.11</v>
       </c>
       <c r="E19" t="n">
-        <v>343</v>
+        <v>190</v>
       </c>
       <c r="F19" t="n">
-        <v>193</v>
+        <v>128</v>
       </c>
       <c r="G19" t="n">
-        <v>2263</v>
+        <v>1081</v>
       </c>
       <c r="H19" t="n">
-        <v>14.12</v>
+        <v>4.92</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>47400</v>
+        <v>18530</v>
       </c>
       <c r="K19" t="n">
-        <v>46350</v>
+        <v>18950</v>
       </c>
       <c r="L19" t="n">
-        <v>47850</v>
+        <v>19870</v>
       </c>
       <c r="M19" t="n">
-        <v>45450</v>
+        <v>17880</v>
       </c>
       <c r="N19" t="n">
-        <v>14.1</v>
+        <v>3.81</v>
       </c>
       <c r="O19" t="n">
-        <v>39390431800</v>
+        <v>275845038355</v>
       </c>
       <c r="P19" t="n">
-        <v>69200</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>24150</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-17000</v>
+        <v>-435000</v>
       </c>
       <c r="S19" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
+          <t>미국 광통신 주가 강세 영향. 젠슨 황의 광통신 투자 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['FDA', '간암', '공매도']</t>
+          <t>['광통신', '미국 주가', '젠슨 황']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,38 +2212,38 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12380</v>
+        <v>45900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.84%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.88</v>
+        <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>71</v>
+        <v>349</v>
       </c>
       <c r="F20" t="n">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="G20" t="n">
-        <v>215</v>
+        <v>2308</v>
       </c>
       <c r="H20" t="n">
-        <v>1.42</v>
+        <v>14.12</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,47 +2251,47 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13010</v>
+        <v>47400</v>
       </c>
       <c r="K20" t="n">
-        <v>12330</v>
+        <v>46350</v>
       </c>
       <c r="L20" t="n">
-        <v>13560</v>
+        <v>47850</v>
       </c>
       <c r="M20" t="n">
-        <v>12220</v>
+        <v>45450</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="O20" t="n">
-        <v>37608768725</v>
+        <v>39965196050</v>
       </c>
       <c r="P20" t="n">
-        <v>22250</v>
+        <v>69200</v>
       </c>
       <c r="Q20" t="n">
-        <v>6000</v>
+        <v>24150</v>
       </c>
       <c r="R20" t="n">
-        <v>-170000</v>
+        <v>-17000</v>
       </c>
       <c r="S20" t="n">
-        <v>13000</v>
+        <v>3000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>기타법인 자사주 매집, 비만치료제 개발 언급 있으나 유증 및 신주 상장 물량 부담 존재. 주가 조작 의혹 제기.</t>
+          <t>FDA 승인 가능성 90% 이상 전망 및 2~3조원 매출 기대감. 공매도와의 공방 속 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['유증', '신주상장', '자사주매집']</t>
+          <t>['FDA', '간암', '공매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30200</v>
+        <v>30100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-5.20%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F21" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G21" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H21" t="n">
         <v>10.78</v>
@@ -2358,7 +2358,7 @@
         <v>10.77</v>
       </c>
       <c r="O21" t="n">
-        <v>93640848300</v>
+        <v>94746815050</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 열위, 기관/외인 매도세 심화 및 급락 우려.</t>
+          <t>경쟁사 대비 부진한 주가 흐름과 기관/외인 매도 물량 출회. 하락 추세 지속.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['급락', '매도', '비교']</t>
+          <t>['주가', '기관', '외인']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>12860</v>
+        <v>12580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-6.27%</t>
+          <t>'-8.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.43</v>
       </c>
       <c r="E22" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F22" t="n">
         <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H22" t="n">
         <v>2.04</v>
@@ -2444,13 +2444,13 @@
         <v>14650</v>
       </c>
       <c r="M22" t="n">
-        <v>12600</v>
+        <v>12560</v>
       </c>
       <c r="N22" t="n">
         <v>2.47</v>
       </c>
       <c r="O22" t="n">
-        <v>56621867025</v>
+        <v>57400086795</v>
       </c>
       <c r="P22" t="n">
         <v>39600</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>우주항공 테마로 언급되며 발사 성공 재료 소멸 우려. 공매도 및 높은 변동성에 대한 불안감 표출.</t>
+          <t>누리호 발사 성공에도 불구하고 재료 소멸 및 급락. 주포 이탈 가능성 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['우주항공', '재료소멸']</t>
+          <t>['누리호', '재료소멸', '급락']</t>
         </is>
       </c>
       <c r="X22" t="n">
